--- a/backtest_runs/20260410_193731/by_symbol/IDRT/IDRT.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/IDRT/IDRT.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
         <v>-5143.860000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>94856.14</v>
@@ -771,7 +771,7 @@
         <v>-3931.080000000005</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>90925.06</v>
@@ -817,7 +817,7 @@
         <v>-836.399999999997</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>90088.66</v>
@@ -955,7 +955,7 @@
         <v>-2425.559999999993</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>96570.75999999999</v>
@@ -1093,7 +1093,7 @@
         <v>-2801.940000000007</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>97741.71999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-2927.399999999997</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>102843.76</v>
@@ -1231,7 +1231,7 @@
         <v>-8573.100000000002</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>94270.66</v>
@@ -1369,7 +1369,7 @@
         <v>-4767.480000000002</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>107569.42</v>
